--- a/examples/Financial-Summary.xlsx
+++ b/examples/Financial-Summary.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,17 +28,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,9 +65,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -143,6 +168,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1600" b="1"/>
               <a:t>Quarterly Departmental Spending</a:t>
             </a:r>
           </a:p>
@@ -277,7 +303,8 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -291,13 +318,13 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3600000"/>
+    <ext cx="7920000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
+        <cNvPr id="1" name="Chart 1" descr="Clustered column chart displaying quarterly departmental spending in USD from Q1 through Q4 across Engineering, Marketing, Operations, and Sales." title="Quarterly Departmental Spending"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
@@ -317,13 +344,13 @@
   <autoFilter ref="A1:F5"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Department"/>
-    <tableColumn id="2" name="Q1_USD"/>
-    <tableColumn id="3" name="Q2_USD"/>
-    <tableColumn id="4" name="Q3_USD"/>
-    <tableColumn id="5" name="Q4_USD"/>
-    <tableColumn id="6" name="Total_USD"/>
+    <tableColumn id="2" name="Q1 (USD)"/>
+    <tableColumn id="3" name="Q2 (USD)"/>
+    <tableColumn id="4" name="Q3 (USD)"/>
+    <tableColumn id="5" name="Q4 (USD)"/>
+    <tableColumn id="6" name="Total (USD)"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -618,124 +645,132 @@
   </sheetPr>
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Q1_USD</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Q2_USD</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Q3_USD</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Q4_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_USD</t>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Q1 (USD)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Q2 (USD)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Q3 (USD)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Q4 (USD)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Total (USD)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="4" t="n">
         <v>120000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="4" t="n">
         <v>135000</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="4" t="n">
         <v>140000</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="4" t="n">
         <v>155000</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="4" t="n">
         <v>550000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="4" t="n">
         <v>45000</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="4" t="n">
         <v>52000</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="4" t="n">
         <v>60000</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="4" t="n">
         <v>207000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="4" t="n">
         <v>80000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="4" t="n">
         <v>82000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="4" t="n">
         <v>85000</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="4" t="n">
         <v>90000</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="4" t="n">
         <v>337000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="4" t="n">
         <v>95000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="4" t="n">
         <v>110000</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="4" t="n">
         <v>115000</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="4" t="n">
         <v>130000</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="4" t="n">
         <v>450000</v>
       </c>
     </row>

--- a/examples/Financial-Summary.xlsx
+++ b/examples/Financial-Summary.xlsx
@@ -30,27 +30,19 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="000F172A"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -67,10 +59,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/examples/Financial-Summary.xlsx
+++ b/examples/Financial-Summary.xlsx
@@ -30,19 +30,27 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,10 +67,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/examples/Financial-Summary.xlsx
+++ b/examples/Financial-Summary.xlsx
@@ -67,16 +67,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -157,7 +157,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -350,7 +349,7 @@
     <tableColumn id="5" name="Q4 (USD)"/>
     <tableColumn id="6" name="Total (USD)"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 

--- a/examples/Financial-Summary.xlsx
+++ b/examples/Financial-Summary.xlsx
@@ -30,7 +30,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0F2942"/>
       <sz val="12"/>
     </font>
     <font>
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F497D"/>
-        <bgColor rgb="FF1F497D"/>
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -349,7 +349,7 @@
     <tableColumn id="5" name="Q4 (USD)"/>
     <tableColumn id="6" name="Total (USD)"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
